--- a/stories/arbres/ATOM-REL.CON.002-03.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yasmine est dans la cour. La maîtresse est près du banc. Yasmine tient un cerceau. Un camarade arrive vite. Il bouscule Yasmine. Yasmine dit : stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Yasmine marche vers la maîtresse. Elle dit : on m'a bousculée. La maîtresse l'écoute. Le soir, papa vient. Yasmine raconte. Papa dit : tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse.</t>
+          <t>Yasmine est dans la cour. La maîtresse est près du banc. Yasmine tient un cerceau. Un camarade arrive vite. Il bouscule Yasmine. Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Yasmine marche vers la maîtresse. On m'a bousculée. La maîtresse l'écoute. Le soir, papa vient. Yasmine raconte. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Yasmine est dans la cour. La maîtresse est près du banc. Yasmine tient un cerceau. Un camarade arrive vite. Il bouscule Yasmine.
+enfant-f|Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse.
+narrateur|Yasmine marche vers la maîtresse.
+narrateur|On m'a bousculée.
+narrateur|La maîtresse l'écoute. Le soir, papa vient. Yasmine raconte.
+papa|Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Yasmine. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Yasmine a dit stop. Elle a su s'éloigner. Elle a rejoint la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Yasmine range le cerceau. Papa lui tend la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-03.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 papa|Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Un camarade bouscule Yasmine. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Yasmine a dit stop. Elle a su s'éloigner. Elle a rejoint la maîtresse.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Yasmine range le cerceau. Papa lui tend la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.002-03.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yasmine dit stop</t>
+          <t>Mila dit stop</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila tient un cerceau jaune. Un camarade passe trop près. Mila dit stop, s'éloigne, rejoint la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yasmine est dans la cour. La maîtresse est près du banc. Yasmine tient un cerceau. Un camarade arrive vite. Il bouscule Yasmine. Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Yasmine marche vers la maîtresse. On m'a bousculée. La maîtresse l'écoute. Le soir, papa vient. Yasmine raconte. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse.</t>
+          <t>Un cerceau jaune s'appuie au grillage. Une goutte brille sur le métal. Le jaune est pâle, tout doux. Un oiseau saute dans l'herbe. L'herbe est un peu mouillée. Elle sent le vert. Papa pose le sac près du banc. Tu vois l'oiseau, Mila ? Oui, papa. Il est petit. Il saute. Je reviens ce soir. D'accord. La main de papa est chaude. La maîtresse est près du banc. En ce moment, Mila est dans la cour. Mila tient le cerceau jaune. Le cerceau est lisse. Il est un peu froid. Il est rond. Mila le fait rouler. Le cerceau fait un petit cercle. Puis il s'arrête dans l'herbe. Un camarade arrive vite. Il passe trop près. Mila sent ses pieds bouger. Son cœur tape. Stop. Mila fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Mila marche vers le banc. On m'a bousculée. La maîtresse l'écoute. Mila reste près d'elle. Elle pose une main sur le banc. Le bois est tiède. Je reste ici. Le cerceau jaune attend dans l'herbe. L'oiseau n'est plus là. Mila souffle. Son cœur tape moins vite. Le soir, papa revient. Mila touche le cerceau une dernière fois. Le métal est moins froid. Tu as joué au cerceau ? Oui. Un camarade trop près. J'ai dit stop. J'ai vu la maîtresse. Bravo, Mila. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. C'est du bon travail. Tu vas bien ? Oui, papa. Stop. Puis la maîtresse. Papa prend sa main. Le cerceau jaune brille encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Yasmine est dans la cour. La maîtresse est près du banc. Yasmine tient un cerceau. Un camarade arrive vite. Il bouscule Yasmine.
-enfant-f|Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse.
-narrateur|Yasmine marche vers la maîtresse.
-narrateur|On m'a bousculée.
-narrateur|La maîtresse l'écoute. Le soir, papa vient. Yasmine raconte.
-papa|Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse.</t>
+          <t>narrateur|Un cerceau jaune s'appuie au grillage.
+narrateur|Une goutte brille sur le métal.
+narrateur|Le jaune est pâle, tout doux.
+narrateur|Un oiseau saute dans l'herbe.
+narrateur|L'herbe est un peu mouillée.
+narrateur|Elle sent le vert.
+narrateur|Papa pose le sac près du banc.
+papa|Tu vois l'oiseau, Mila ?
+enfant-f|Oui, papa.
+papa|Il est petit.
+enfant-f|Il saute.
+papa|Je reviens ce soir.
+enfant-f|D'accord.
+narrateur|La main de papa est chaude.
+narrateur|La maîtresse est près du banc.
+narrateur|En ce moment, Mila est dans la cour.
+narrateur|Mila tient le cerceau jaune.
+narrateur|Le cerceau est lisse.
+narrateur|Il est un peu froid.
+enfant-f|Il est rond.
+narrateur|Mila le fait rouler.
+narrateur|Le cerceau fait un petit cercle.
+narrateur|Puis il s'arrête dans l'herbe.
+narrateur|Un camarade arrive vite.
+narrateur|Il passe trop près.
+narrateur|Mila sent ses pieds bouger.
+narrateur|Son cœur tape.
+enfant-f|Stop.
+narrateur|Mila fait un pas.
+narrateur|Elle peut s'éloigner.
+narrateur|S'éloigner, c'est aller vers la maîtresse.
+narrateur|Mila marche vers le banc.
+enfant-f|On m'a bousculée.
+narrateur|La maîtresse l'écoute.
+narrateur|Mila reste près d'elle.
+narrateur|Elle pose une main sur le banc.
+narrateur|Le bois est tiède.
+enfant-f|Je reste ici.
+narrateur|Le cerceau jaune attend dans l'herbe.
+narrateur|L'oiseau n'est plus là.
+narrateur|Mila souffle.
+narrateur|Son cœur tape moins vite.
+narrateur|Le soir, papa revient.
+narrateur|Mila touche le cerceau une dernière fois.
+narrateur|Le métal est moins froid.
+papa|Tu as joué au cerceau ?
+enfant-f|Oui.
+enfant-f|Un camarade trop près.
+enfant-f|J'ai dit stop.
+enfant-f|J'ai vu la maîtresse.
+papa|Bravo, Mila.
+papa|Tu as dit stop.
+papa|Tu t'es éloignée.
+papa|Tu es allée vers la maîtresse.
+papa|C'est du bon travail.
+papa|Tu vas bien ?
+enfant-f|Oui, papa.
+enfant-f|Stop.
+enfant-f|Puis la maîtresse.
+narrateur|Papa prend sa main.
+narrateur|Le cerceau jaune brille encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1345,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Un camarade bouscule Yasmine. Que fait-elle ?</t>
+          <t>Un camarade bouscule Mila. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1568,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade bouscule Yasmine. Que fait-elle ?</t>
+          <t>narrateur|Un camarade bouscule Mila.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Yasmine a dit stop. Elle a su s'éloigner. Elle a rejoint la maîtresse.</t>
+          <t>Mila a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. C'est le bon geste. Stop. Puis la maîtresse. Oui. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1741,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Yasmine a dit stop. Elle a su s'éloigner. Elle a rejoint la maîtresse.</t>
+          <t>narrateur|Mila a dit stop.
+narrateur|Elle s'est éloignée.
+narrateur|Elle a rejoint la maîtresse.
+papa|Bravo.
+papa|C'est le bon geste.
+enfant-f|Stop.
+enfant-f|Puis la maîtresse.
+papa|Oui.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Yasmine range le cerceau. Papa lui tend la main.</t>
+          <t>Mila range le cerceau. Le métal est encore froid. Je te tends la main. Oui, papa. Papa marche à côté. On rentre ? Oui. L'oiseau est parti ? Oui. L'herbe brille un peu. Le grillage est calme. Le cerceau reste là ? Oui, papa. Une goutte n'est plus sur le métal.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,7 +1917,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Yasmine range le cerceau. Papa lui tend la main.</t>
+          <t>narrateur|Mila range le cerceau.
+narrateur|Le métal est encore froid.
+papa|Je te tends la main.
+enfant-f|Oui, papa.
+narrateur|Papa marche à côté.
+papa|On rentre ?
+enfant-f|Oui.
+papa|L'oiseau est parti ?
+enfant-f|Oui.
+narrateur|L'herbe brille un peu.
+narrateur|Le grillage est calme.
+papa|Le cerceau reste là ?
+enfant-f|Oui, papa.
+narrateur|Une goutte n'est plus sur le métal.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1869,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Mila. Tu as fait du bon travail. Le cerceau jaune s'appuie au grillage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,7 +2098,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit stop.
+enfant-f|Je suis allée vers la maîtresse.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le cerceau jaune s'appuie au grillage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2031,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-03.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un cerceau jaune s'appuie au grillage. Une goutte brille sur le métal. Le jaune est pâle, tout doux. Un oiseau saute dans l'herbe. L'herbe est un peu mouillée. Elle sent le vert. Papa pose le sac près du banc. Tu vois l'oiseau, Mila ? Oui, papa. Il est petit. Il saute. Je reviens ce soir. D'accord. La main de papa est chaude. La maîtresse est près du banc. En ce moment, Mila est dans la cour. Mila tient le cerceau jaune. Le cerceau est lisse. Il est un peu froid. Il est rond. Mila le fait rouler. Le cerceau fait un petit cercle. Puis il s'arrête dans l'herbe. Un camarade arrive vite. Il passe trop près. Mila sent ses pieds bouger. Son cœur tape. Stop. Mila fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Mila marche vers le banc. On m'a bousculée. La maîtresse l'écoute. Mila reste près d'elle. Elle pose une main sur le banc. Le bois est tiède. Je reste ici. Le cerceau jaune attend dans l'herbe. L'oiseau n'est plus là. Mila souffle. Son cœur tape moins vite. Le soir, papa revient. Mila touche le cerceau une dernière fois. Le métal est moins froid. Tu as joué au cerceau ? Oui. Un camarade trop près. J'ai dit stop. J'ai vu la maîtresse. Bravo, Mila. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. C'est du bon travail. Tu vas bien ? Oui, papa. Stop. Puis la maîtresse. Papa prend sa main. Le cerceau jaune brille encore.</t>
+          <t>Un cerceau jaune s'appuie au grillage. Une goutte brille sur le métal. Le jaune est pâle, tout doux. Un oiseau saute dans l'herbe. L'herbe est un peu mouillée. Elle sent le vert. Papa pose le sac près du banc. Tu vois l'oiseau, Mila ? Oui, papa. Il est petit. Il saute. Je reviens ce soir. D'accord. La main de papa est chaude. La maîtresse est près du banc. En ce moment, Mila est dans la cour. Mila tient le cerceau jaune. Le cerceau est lisse. Il est un peu froid. Il est rond. Mila le fait rouler. Le cerceau fait un petit cercle. Puis il s'arrête dans l'herbe. Un camarade arrive vite. Il passe trop près. Mila sent ses pieds bouger. Son cœur tape. Stop. Mila fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Mila marche vers le banc. On m'a bousculée. La maîtresse l'écoute. Mila reste près d'elle. Elle pose une main sur le banc. Le bois est tiède. Je reste ici. Le cerceau jaune attend dans l'herbe. L'oiseau n'est plus là. Mila souffle. Son cœur tape moins vite. Le soir, papa revient. Mila touche le cerceau une dernière fois. Le métal est moins froid. Tu as joué au cerceau ? Oui. Un camarade trop près. J'ai dit stop. J'ai vu la maîtresse. Bravo, Mila. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Tu vas bien ? Oui, papa. Stop. Puis la maîtresse. Papa prend sa main. Le cerceau jaune brille encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Yasmine est dans la cour. La maîtresse est près du banc. Yasmine tient un cerceau. Un camarade arrive vite. Il bouscule Yasmine. Yasmine dit : &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Yasmine marche vers la maîtresse. Elle dit : on m'a bousculée. La maîtresse l'écoute. Le soir, papa vient. Yasmine raconte. Papa dit : tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un cerceau jaune s'appuie au grillage. Une goutte brille sur le métal. Le jaune est pâle, tout doux. Un oiseau saute dans l'herbe. L'herbe est un peu mouillée. Elle sent le vert. Papa pose le sac près du banc. Tu vois l'oiseau, Mila ? Oui, papa. Il est petit. Il saute. Je reviens ce soir. D'accord. La main de papa est chaude. La maîtresse est près du banc. En ce moment, Mila est dans la cour. Mila tient le cerceau jaune. Le cerceau est lisse. Il est un peu froid. Il est rond. Mila le fait rouler. Le cerceau fait un petit cercle. Puis il s'arrête dans l'herbe. Un camarade arrive vite. Il passe trop près. Mila sent ses pieds bouger. Son cœur tape. Stop. Mila fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Mila marche vers le banc. On m'a bousculée. La maîtresse l'écoute. Mila reste près d'elle. Elle pose une main sur le banc. Le bois est tiède. Je reste ici. Le cerceau jaune attend dans l'herbe. L'oiseau n'est plus là. Mila souffle. Son cœur tape moins vite. Le soir, papa revient. Mila touche le cerceau une dernière fois. Le métal est moins froid. Tu as joué au cerceau ? Oui. Un camarade trop près. J'ai dit stop. J'ai vu la maîtresse. Bravo, Mila. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Tu vas bien ? Oui, papa. Stop. Puis la maîtresse. Papa prend sa main. Le cerceau jaune brille encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1378,7 +1378,6 @@
 papa|Tu as dit stop.
 papa|Tu t'es éloignée.
 papa|Tu es allée vers la maîtresse.
-papa|C'est du bon travail.
 papa|Tu vas bien ?
 enfant-f|Oui, papa.
 enfant-f|Stop.
@@ -1387,7 +1386,6 @@
 narrateur|Le cerceau jaune brille encore.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1417,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Un camarade bouscule Yasmine. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade bouscule Mila. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1572,7 +1570,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1597,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. C'est le bon geste. Stop. Puis la maîtresse. Oui. Tu as fait du bon travail.</t>
+          <t>Mila a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. C'est le bon geste. Stop. Puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Yasmine a dit &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Elle a su s'éloigner. Elle a rejoint la maîtresse.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. C'est le bon geste. Stop. Puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,11 +1745,9 @@
 papa|C'est le bon geste.
 enfant-f|Stop.
 enfant-f|Puis la maîtresse.
-papa|Oui.
-papa|Tu as fait du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+papa|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1782,7 +1777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Yasmine range le cerceau. Papa lui tend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila range le cerceau. Le métal est encore froid. Je te tends la main. Oui, papa. Papa marche à côté. On rentre ? Oui. L'oiseau est parti ? Oui. L'herbe brille un peu. Le grillage est calme. Le cerceau reste là ? Oui, papa. Une goutte n'est plus sur le métal.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1933,7 +1928,6 @@
 narrateur|Une goutte n'est plus sur le métal.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1958,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Mila. Tu as fait du bon travail. Le cerceau jaune s'appuie au grillage. L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Mila. Le cerceau jaune s'appuie au grillage.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Mila. Le cerceau jaune s'appuie au grillage.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,12 +2095,9 @@
           <t>enfant-f|J'ai dit stop.
 enfant-f|Je suis allée vers la maîtresse.
 papa|Bravo, Mila.
-papa|Tu as fait du bon travail.
-narrateur|Le cerceau jaune s'appuie au grillage.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le cerceau jaune s'appuie au grillage.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2125,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2161,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-03.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yasmine, maîtresse, papa</t>
+          <t>Mila, maîtresse, papa</t>
         </is>
       </c>
     </row>
